--- a/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0001T0006Z000C1N9_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0001T0006Z000C1N9_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>3.359666618989892</v>
+        <v>0.5459458255858575</v>
       </c>
       <c r="D2" t="n">
-        <v>4.019876703915603</v>
+        <v>0.6532299643862856</v>
       </c>
       <c r="E2" t="n">
-        <v>13.89002641527397</v>
+        <v>2.25712929248202</v>
       </c>
       <c r="F2" t="n">
-        <v>13.9031571803149</v>
+        <v>2.259263041801171</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>34.83828066232699</v>
+        <v>5.661220607628136</v>
       </c>
       <c r="D3" t="n">
-        <v>34.50184218596265</v>
+        <v>5.606549355218931</v>
       </c>
       <c r="E3" t="n">
-        <v>13.89002641527397</v>
+        <v>2.25712929248202</v>
       </c>
       <c r="F3" t="n">
-        <v>13.9031571803149</v>
+        <v>2.259263041801171</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>8.733432835724162</v>
+        <v>1.419182835805176</v>
       </c>
       <c r="D4" t="n">
-        <v>9.075029201886647</v>
+        <v>1.47469224530658</v>
       </c>
       <c r="E4" t="n">
-        <v>13.89002641527397</v>
+        <v>2.25712929248202</v>
       </c>
       <c r="F4" t="n">
-        <v>13.9031571803149</v>
+        <v>2.259263041801171</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>47.73751871561915</v>
+        <v>7.757346791288112</v>
       </c>
       <c r="D5" t="n">
-        <v>47.44265987498688</v>
+        <v>7.709432229685368</v>
       </c>
       <c r="E5" t="n">
-        <v>13.89002641527397</v>
+        <v>2.25712929248202</v>
       </c>
       <c r="F5" t="n">
-        <v>13.9031571803149</v>
+        <v>2.259263041801171</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>38.29690517157437</v>
+        <v>6.223247090380836</v>
       </c>
       <c r="D6" t="n">
-        <v>38.79429916566583</v>
+        <v>6.304073614420697</v>
       </c>
       <c r="E6" t="n">
-        <v>13.89002641527397</v>
+        <v>2.25712929248202</v>
       </c>
       <c r="F6" t="n">
-        <v>13.9031571803149</v>
+        <v>2.259263041801171</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>30.55700430096602</v>
+        <v>4.965513198906979</v>
       </c>
       <c r="D7" t="n">
-        <v>30.72167608426528</v>
+        <v>4.992272363693108</v>
       </c>
       <c r="E7" t="n">
-        <v>13.89002641527397</v>
+        <v>2.25712929248202</v>
       </c>
       <c r="F7" t="n">
-        <v>13.9031571803149</v>
+        <v>2.259263041801171</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>46.44235103566391</v>
+        <v>7.546882043295386</v>
       </c>
       <c r="D8" t="n">
-        <v>46.41253116545597</v>
+        <v>7.542036314386594</v>
       </c>
       <c r="E8" t="n">
-        <v>13.89002641527397</v>
+        <v>2.25712929248202</v>
       </c>
       <c r="F8" t="n">
-        <v>13.9031571803149</v>
+        <v>2.259263041801171</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>36.07985206518627</v>
+        <v>5.862975960592769</v>
       </c>
       <c r="D9" t="n">
-        <v>37.32284120721283</v>
+        <v>6.064961696172085</v>
       </c>
       <c r="E9" t="n">
-        <v>13.89002641527397</v>
+        <v>2.25712929248202</v>
       </c>
       <c r="F9" t="n">
-        <v>13.9031571803149</v>
+        <v>2.259263041801171</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>18.46069121169867</v>
+        <v>2.999862321901035</v>
       </c>
       <c r="D10" t="n">
-        <v>19.64863871912273</v>
+        <v>3.192903791857443</v>
       </c>
       <c r="E10" t="n">
-        <v>13.89002641527397</v>
+        <v>2.25712929248202</v>
       </c>
       <c r="F10" t="n">
-        <v>13.9031571803149</v>
+        <v>2.259263041801171</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>42.53963777309164</v>
+        <v>6.912691138127392</v>
       </c>
       <c r="D11" t="n">
-        <v>43.8648594260459</v>
+        <v>7.128039656732458</v>
       </c>
       <c r="E11" t="n">
-        <v>13.89002641527397</v>
+        <v>2.25712929248202</v>
       </c>
       <c r="F11" t="n">
-        <v>13.9031571803149</v>
+        <v>2.259263041801171</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>53.12612389971073</v>
+        <v>8.632995133702995</v>
       </c>
       <c r="D12" t="n">
-        <v>54.48387040125768</v>
+        <v>8.853628940204372</v>
       </c>
       <c r="E12" t="n">
-        <v>13.89002641527397</v>
+        <v>2.25712929248202</v>
       </c>
       <c r="F12" t="n">
-        <v>13.9031571803149</v>
+        <v>2.259263041801171</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>38.65092685604728</v>
+        <v>6.280775614107684</v>
       </c>
       <c r="D13" t="n">
-        <v>37.27859685427809</v>
+        <v>6.057771988820189</v>
       </c>
       <c r="E13" t="n">
-        <v>13.89002641527397</v>
+        <v>2.25712929248202</v>
       </c>
       <c r="F13" t="n">
-        <v>13.9031571803149</v>
+        <v>2.259263041801171</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>30.33388762295896</v>
+        <v>4.929256738730832</v>
       </c>
       <c r="D14" t="n">
-        <v>30.95742026018841</v>
+        <v>5.030580792280618</v>
       </c>
       <c r="E14" t="n">
-        <v>13.89002641527397</v>
+        <v>2.25712929248202</v>
       </c>
       <c r="F14" t="n">
-        <v>13.9031571803149</v>
+        <v>2.259263041801171</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>23.18475779436885</v>
+        <v>3.767523141584938</v>
       </c>
       <c r="D15" t="n">
-        <v>24.49601273050178</v>
+        <v>3.98060206870654</v>
       </c>
       <c r="E15" t="n">
-        <v>13.89002641527397</v>
+        <v>2.25712929248202</v>
       </c>
       <c r="F15" t="n">
-        <v>13.9031571803149</v>
+        <v>2.259263041801171</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>6.959292499961189</v>
+        <v>1.130885031243693</v>
       </c>
       <c r="D16" t="n">
-        <v>7.585102158081252</v>
+        <v>1.232579100688203</v>
       </c>
       <c r="E16" t="n">
-        <v>13.89002641527397</v>
+        <v>2.25712929248202</v>
       </c>
       <c r="F16" t="n">
-        <v>13.9031571803149</v>
+        <v>2.259263041801171</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>8.831400344643317</v>
+        <v>1.435102556004539</v>
       </c>
       <c r="D17" t="n">
-        <v>9.100729909723832</v>
+        <v>1.478868610330123</v>
       </c>
       <c r="E17" t="n">
-        <v>13.89002641527397</v>
+        <v>2.25712929248202</v>
       </c>
       <c r="F17" t="n">
-        <v>13.9031571803149</v>
+        <v>2.259263041801171</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>35.8670298054064</v>
+        <v>5.828392343378541</v>
       </c>
       <c r="D18" t="n">
-        <v>35.65807421000698</v>
+        <v>5.794437059126134</v>
       </c>
       <c r="E18" t="n">
-        <v>13.89002641527397</v>
+        <v>2.25712929248202</v>
       </c>
       <c r="F18" t="n">
-        <v>13.9031571803149</v>
+        <v>2.259263041801171</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>7.01634041686511</v>
+        <v>1.14015531774058</v>
       </c>
       <c r="D19" t="n">
-        <v>6.506716153000541</v>
+        <v>1.057341374862588</v>
       </c>
       <c r="E19" t="n">
-        <v>13.89002641527397</v>
+        <v>2.25712929248202</v>
       </c>
       <c r="F19" t="n">
-        <v>13.9031571803149</v>
+        <v>2.259263041801171</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>20.56845655339674</v>
+        <v>3.34237418992697</v>
       </c>
       <c r="D20" t="n">
-        <v>20.11351859117335</v>
+        <v>3.26844677106567</v>
       </c>
       <c r="E20" t="n">
-        <v>13.89002641527397</v>
+        <v>2.25712929248202</v>
       </c>
       <c r="F20" t="n">
-        <v>13.9031571803149</v>
+        <v>2.259263041801171</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>18.62693167986946</v>
+        <v>3.026876397978787</v>
       </c>
       <c r="D21" t="n">
-        <v>18.01873330541877</v>
+        <v>2.92804416213055</v>
       </c>
       <c r="E21" t="n">
-        <v>13.89002641527397</v>
+        <v>2.25712929248202</v>
       </c>
       <c r="F21" t="n">
-        <v>13.9031571803149</v>
+        <v>2.259263041801171</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>26.77607650676806</v>
+        <v>4.351112432349809</v>
       </c>
       <c r="D22" t="n">
-        <v>26.16391685595822</v>
+        <v>4.251636489093212</v>
       </c>
       <c r="E22" t="n">
-        <v>13.89002641527397</v>
+        <v>2.25712929248202</v>
       </c>
       <c r="F22" t="n">
-        <v>13.9031571803149</v>
+        <v>2.259263041801171</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>29.35102582743226</v>
+        <v>4.769541696957743</v>
       </c>
       <c r="D23" t="n">
-        <v>28.81311695227684</v>
+        <v>4.682131504744986</v>
       </c>
       <c r="E23" t="n">
-        <v>13.89002641527397</v>
+        <v>2.25712929248202</v>
       </c>
       <c r="F23" t="n">
-        <v>13.9031571803149</v>
+        <v>2.259263041801171</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>32.68625824743795</v>
+        <v>5.311516965208667</v>
       </c>
       <c r="D24" t="n">
-        <v>32.28878174866803</v>
+        <v>5.246927034158555</v>
       </c>
       <c r="E24" t="n">
-        <v>13.89002641527397</v>
+        <v>2.25712929248202</v>
       </c>
       <c r="F24" t="n">
-        <v>13.9031571803149</v>
+        <v>2.259263041801171</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>39.96928617884577</v>
+        <v>6.495009004062438</v>
       </c>
       <c r="D25" t="n">
-        <v>39.4827359050463</v>
+        <v>6.415944584570023</v>
       </c>
       <c r="E25" t="n">
-        <v>13.89002641527397</v>
+        <v>2.25712929248202</v>
       </c>
       <c r="F25" t="n">
-        <v>13.9031571803149</v>
+        <v>2.259263041801171</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
